--- a/survey_templates/039_public_space_usage_survey_form--survey_templates.xlsx
+++ b/survey_templates/039_public_space_usage_survey_form--survey_templates.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -927,12 +927,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>email</t>
+          <t>email_2</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>email</t>
+          <t>Email 2</t>
         </is>
       </c>
       <c r="D21" t="inlineStr"/>
@@ -950,12 +950,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>phone</t>
+          <t>phone_2</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>phone</t>
+          <t>Phone 2</t>
         </is>
       </c>
       <c r="D22" t="inlineStr"/>
@@ -973,12 +973,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>organization</t>
+          <t>organization_2</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>organization</t>
+          <t>Organization 2</t>
         </is>
       </c>
       <c r="D23" t="inlineStr"/>
@@ -996,12 +996,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>comments</t>
+          <t>comments_2</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>comments</t>
+          <t>Comments 2</t>
         </is>
       </c>
       <c r="D24" t="inlineStr"/>
@@ -1019,12 +1019,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>favorite_space</t>
+          <t>favorite_space_2</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>favorite space</t>
+          <t>Favorite Space 2</t>
         </is>
       </c>
       <c r="D25" t="inlineStr"/>
@@ -1042,12 +1042,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>favorite_space_others</t>
+          <t>favorite_space_others_2</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>favorite space others</t>
+          <t>Favorite Space Others 2</t>
         </is>
       </c>
       <c r="D26" t="inlineStr"/>
@@ -1065,12 +1065,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>time_in_public_space</t>
+          <t>time_in_public_space_2</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>time in public space</t>
+          <t>Time In Public Space 2</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -1092,12 +1092,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>visit_frequency</t>
+          <t>visit_frequency_2</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>visit frequency</t>
+          <t>Visit Frequency 2</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -1119,12 +1119,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>favorite_feature</t>
+          <t>favorite_feature_2</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>favorite feature</t>
+          <t>Favorite Feature 2</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -1152,7 +1152,7 @@
   <dimension ref="A1:C29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="26" customWidth="1" min="1" max="1"/>
+    <col width="28" customWidth="1" min="1" max="1"/>
     <col width="15" customWidth="1" min="2" max="2"/>
     <col width="15" customWidth="1" min="3" max="3"/>
   </cols>
@@ -1432,7 +1432,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>favorite_space_choices</t>
+          <t>favorite_space_2_choices</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1449,7 +1449,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>favorite_space_choices</t>
+          <t>favorite_space_2_choices</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1466,7 +1466,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>favorite_space_choices</t>
+          <t>favorite_space_2_choices</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1483,7 +1483,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>favorite_space_choices</t>
+          <t>favorite_space_2_choices</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1500,7 +1500,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>visit_frequency_choices</t>
+          <t>visit_frequency_2_choices</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1517,7 +1517,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>visit_frequency_choices</t>
+          <t>visit_frequency_2_choices</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1534,7 +1534,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>visit_frequency_choices</t>
+          <t>visit_frequency_2_choices</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1551,7 +1551,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>favorite_feature_choices</t>
+          <t>favorite_feature_2_choices</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1568,7 +1568,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>favorite_feature_choices</t>
+          <t>favorite_feature_2_choices</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1585,7 +1585,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>favorite_feature_choices</t>
+          <t>favorite_feature_2_choices</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1602,7 +1602,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>favorite_feature_choices</t>
+          <t>favorite_feature_2_choices</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1619,7 +1619,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>favorite_feature_choices</t>
+          <t>favorite_feature_2_choices</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1636,7 +1636,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>favorite_feature_choices</t>
+          <t>favorite_feature_2_choices</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
